--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd7a0fbdebc0a4c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6a8687de8e34851"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6a8687de8e34851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21d055a832124478"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21d055a832124478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re11999f0483f40b5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re11999f0483f40b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f32a2323ce144e1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f32a2323ce144e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra8b3417a8dc74f67"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra8b3417a8dc74f67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e15035a12284e43"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e15035a12284e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f8d8d1954214b1b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f8d8d1954214b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e6f1122ea0f40f7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e6f1122ea0f40f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6208a9af8144e36"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6208a9af8144e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b29cc65742a41c9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b29cc65742a41c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc291d34bd5994fbc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc291d34bd5994fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e92fc67bbf04a75"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e92fc67bbf04a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb08bd71db34d80"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb08bd71db34d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45acc8d085d54518"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45acc8d085d54518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c0179b34efb40c9"/>
   </x:sheets>
 </x:workbook>
 </file>
